--- a/data/weapons.xlsx
+++ b/data/weapons.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Tree Index" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weapons" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Melee" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ranged" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -470,7 +471,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Weapons</t>
+          <t>Melee</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -490,7 +491,34 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>transferable fundamentals: measure, timing, footwork, guard</t>
+          <t>Represents transferable fundamentals: measure, timing, reading an opponent, footwork, maintaining guard, committing to a strike, etc. Melee is a parent Constellation: every Talent you buy in Two-Weapon Fighting, Shield Fighting, Brawling, Dueling, Great Weapon Fighting, Spear &amp; Polearm Fighting, or Armored Fighting counts toward your Melee rank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Ranged</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Crit succeed or crit fail on any roll with consequences, directly related to a talent in this constellation.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Represents what transfers between every weapon that leaves the hand: judging distance, timing a release, leading a moving target, and shooting past friends. Ranged is a parent Constellation: every Talent you buy in Archery, Crossbow Fighting, or Missile Skirmishing counts toward your Ranged rank.</t>
         </is>
       </c>
     </row>
@@ -505,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -581,7 +609,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Weapons Training</t>
+          <t>Melee Training</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -594,17 +622,52 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>You are Trained in weapons: add this Constellation's Proficiency Bonus to your attack rolls with any weapon.
-Special Intuitive weapons use your full Weapons Proficiency Bonus. Practiced or Technical weapons do not; see Chapter 5: Equipment for rules on Weapon Handling.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+          <r>
+            <t xml:space="preserve">You are Trained in Melee: add this Constellation's Proficiency Bonus to your attack rolls with any weapon in your hand, and to Gain Control. You gain the </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Counter ❶↺</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> and </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Intercept ❶↺</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Reactions.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Special</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Intuitive weapons use your full Melee Proficiency Bonus. Practiced or Technical weapons do not; see Chapter 5: Equipment for rules on Weapon Traits.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -617,21 +680,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Weapons Training</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+          <t>Melee Training</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Choose a Weapon Group or a Technical weapon. You are Familiar with weapons in that group or that Technical weapon.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Weapon Group or Technical Weapon</t>
@@ -649,21 +712,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Weapons Training</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+          <t>Melee Training</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Use a reaction to draw or stow an item, weapon, or shield in each hand (or in both hands, if it requires two hands).</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+          <t>Use a Reaction ⓿↺ to draw or stow an item, weapon, or shield in each hand (or in both hands, if it requires two hands).</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -676,21 +739,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Weapon Familiarity</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>You may deal bludgeoning damage with any Familiar melee weapon you wield, striking with the pommel, the haft, or the flat. Its damage die drops one step when you do (d12 to d10 to d8 to d6 to d4).</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -703,26 +766,26 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Weapon Familiarity</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>+2 circumstance bonus to your Guard against Disarm regarding a Familiar weapon. When a Disarm against you would succeed, you keep hold of the weapon and suffer only the loosened grip.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+          <t>+2 Situation bonus to your Guard against Disarm regarding a Familiar weapon. When a Disarm against you would succeed, you keep hold of the weapon and suffer only the loosened grip.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Read the Steel ◆</t>
+          <t>Read the Steel ❶</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -730,26 +793,26 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Weapons Training</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
+          <t>Melee Training</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Study one creature you can see. Until the end of the encounter you know the Protection and the material of each of its Zones, and your Strikes against it ignore 1 Protection.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Reactive Strike ↺</t>
+          <t>Reactive Strike</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -757,25 +820,318 @@
           <t>E</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Weapon Familiarity</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>You gain the Reactive Strike ↺ reaction.
-Reactive Strike ↺
-Requirements You are wielding a weapon in which you are at least Expert.
-Trigger An Observed creature within your reach begins to use a Manipulate action or Stride.
-Effect Make a melee Strike against the triggering creature. The Multiple Attack Penalty does not apply; nor does it accrue as a result of this Strike. On a Critical Hit, the triggering action is disrupted: it fails, and any actions still to come in that activity are lost.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
+          <t>Your Intercept ❶↺ also triggers when an Observed creature within your Reach begins a Manipulate Maneuver, or a Motion Maneuver that would carry it out of your Reach. You may only use this with weapons in which you are at least Expert. On a Critical Hit, the triggering Maneuver is disrupted: it fails, and any actions still to come in it are lost.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Feeling</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Melee Training</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>You read the pressure in the bind before you commit to it. When your Gain Control Misses, the target does not take Control of your weapon; the Bind is simply neutral.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Winding</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Weapon Familiarity</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>While you Control a foe's weapon, your Committed Strike ❸ against that foe is not Weighted, and your Strikes against that foe do not end the Bind. You cut from the bind without leaving it.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Master Cut</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Weapon Familiarity</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>When you Counter, you gain a +2 Situation bonus to the Defense you roll against the triggering attack. Your parry and your cut are one motion.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="96" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Talent</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Requires</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Prerequisites</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Effect (rich text in this cell mirrors into the app and handbook)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Feeds (blank = tree default)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Grants (restricted TPs this talent gives)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Choice (a build-time pick this talent demands)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Free Talent (handed over, no point spent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ranged Training</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">You are Trained in Ranged: add this Constellation's Proficiency Bonus to your attack rolls with any weapon that leaves your hand: bows, crossbows, slings, and thrown weapons (a dagger uses Melee in your hand and Ranged in the air).
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Special</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Intuitive weapons use your full Ranged Proficiency Bonus. Practiced or Technical weapons do not; see Chapter 5: Equipment.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Aim ❶</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Ranged Training</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Concentrate</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Choose one creature you can Observe within your weapon's range. Your next ranged Strike against it before the end of your next Opportunity gains a +1 Situation bonus, and on a Hit you may choose the Zone it strikes.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Loose and Move</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Ranged Training</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>After making a ranged Strike, you may Step ⓿ once per round.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Steady Release</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Ranged Training</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Your ranged Strikes ignore a target's Lesser Cover (the +1 it grants, and the Zone rule) if you have not Moved this round. Patience finds the gap.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/weapons.xlsx
+++ b/data/weapons.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="7350" yWindow="5745" windowWidth="41880" windowHeight="13980" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Tree Index" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,14 +11,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ranged" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,9 +27,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -42,7 +47,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E5F6B"/>
+        <fgColor rgb="FF0E5F6B"/>
       </patternFill>
     </fill>
   </fills>
@@ -68,7 +73,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -468,7 +473,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="135" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Melee</t>
@@ -495,7 +500,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="120" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Ranged</t>
@@ -533,20 +538,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="10" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -605,8 +607,13 @@
           <t>Free Talent (handed over, no point spent)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Melee Training</t>
@@ -632,32 +639,26 @@
           </r>
           <r>
             <rPr>
-              <rFont val="Calibri"/>
               <b val="1"/>
-              <sz val="11"/>
+            </rPr>
+            <t>Intercept ❶↺</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Reaction. At Expert rank in Melee you also gain the </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
             </rPr>
             <t>Counter ❶↺</t>
           </r>
           <r>
-            <t xml:space="preserve"> and </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Intercept ❶↺</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> Reactions.
+            <t xml:space="preserve"> Reaction.
 </t>
           </r>
           <r>
             <rPr>
-              <rFont val="Calibri"/>
               <b val="1"/>
-              <sz val="11"/>
             </rPr>
             <t>Special</t>
           </r>
@@ -668,8 +669,13 @@
       </c>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
-    </row>
-    <row r="3">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Weapon Familiarity</t>
@@ -701,7 +707,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Quick Draw</t>
@@ -728,7 +734,7 @@
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Turn the Weapon</t>
@@ -755,7 +761,7 @@
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Sure Grip</t>
@@ -782,7 +788,7 @@
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Read the Steel ❶</t>
@@ -809,7 +815,7 @@
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Reactive Strike</t>
@@ -836,7 +842,7 @@
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Feeling</t>
@@ -863,7 +869,7 @@
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Winding</t>
@@ -890,7 +896,7 @@
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Master Cut</t>
@@ -928,20 +934,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="10" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1000,8 +1003,13 @@
           <t>Free Talent (handed over, no point spent)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="75" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Ranged Training</t>
@@ -1035,6 +1043,13 @@
             <t>Special</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> Intuitive weapons use your full Ranged Proficiency Bonus. Practiced or Technical weapons do not; see Chapter 5: Equipment.</t>
           </r>
         </is>
@@ -1042,7 +1057,7 @@
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" ht="45" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Aim ❶</t>
@@ -1072,6 +1087,13 @@
             <t>Concentrate</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> Choose one creature you can Observe within your weapon's range. Your next ranged Strike against it before the end of your next Opportunity gains a +1 Situation bonus, and on a Hit you may choose the Zone it strikes.</t>
           </r>
         </is>
@@ -1106,7 +1128,7 @@
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Steady Release</t>

--- a/data/weapons.xlsx
+++ b/data/weapons.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -549,6 +549,8 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -610,6 +612,11 @@
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
@@ -934,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -945,6 +952,8 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1006,6 +1015,11 @@
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
